--- a/dados cozac.xlsx
+++ b/dados cozac.xlsx
@@ -1849,7 +1849,12 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Não Vendido</t>
+          <t>Proposta em Negociação</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Proposta pelos 8 aptos (78780 até 78787) em R$ 880,00. Estamos tentando chegar em R$ 1M</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2019,7 +2024,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Não Vendido</t>
+          <t>Proposta em Negociação</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2104,7 +2109,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Não Vendido</t>
+          <t>Proposta em Negociação</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2189,7 +2194,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Não Vendido</t>
+          <t>Proposta em Negociação</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2274,7 +2279,7 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Não Vendido</t>
+          <t>Proposta em Negociação</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2359,7 +2364,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Não Vendido</t>
+          <t>Proposta em Negociação</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2444,7 +2449,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Não Vendido</t>
+          <t>Proposta em Negociação</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2529,7 +2534,7 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Não Vendido</t>
+          <t>Proposta em Negociação</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -2784,7 +2789,12 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Não Vendido</t>
+          <t>Proposta em Negociação</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Proposta de R$ 200K pelos 2 imóveis, estamos tentando chegar em R$ 240K (102753 e 102754)</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -2869,7 +2879,7 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Não Vendido</t>
+          <t>Proposta em Negociação</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
